--- a/Assets/100_Data/XlsxFiles/Core_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Core_Data.xlsx
@@ -517,7 +517,7 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -549,7 +549,7 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>17</v>
@@ -581,7 +581,7 @@
         <v>16</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>22</v>
@@ -613,7 +613,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>27</v>
@@ -645,7 +645,7 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>32</v>
@@ -677,7 +677,7 @@
         <v>28</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>37</v>
@@ -709,7 +709,7 @@
         <v>32</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>42</v>

--- a/Assets/100_Data/XlsxFiles/Core_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Core_Data.xlsx
@@ -514,10 +514,10 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>12</v>
@@ -546,10 +546,10 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>17</v>
@@ -578,10 +578,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>22</v>
@@ -610,10 +610,10 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>27</v>
@@ -642,10 +642,10 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>32</v>
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>37</v>
@@ -706,10 +706,10 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>42</v>

--- a/Assets/100_Data/XlsxFiles/Core_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Core_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,6 +107,38 @@
   </si>
   <si>
     <t>UpgradeRequiredDepth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;255;255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>180;180;180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;175;102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120;120;155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;159;211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>148;255;214</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255;198;92</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -175,9 +207,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:J8" totalsRowShown="0">
-  <autoFilter ref="A1:J8"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:K8" totalsRowShown="0">
+  <autoFilter ref="A1:K8"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="DisplayName"/>
@@ -185,6 +217,7 @@
     <tableColumn id="6" name="FacilityCount"/>
     <tableColumn id="7" name="EngineCount"/>
     <tableColumn id="10" name="FactoryLength"/>
+    <tableColumn id="11" name="Color"/>
     <tableColumn id="4" name="UpgradeRequiredDepth"/>
     <tableColumn id="8" name="UpgradeRequiredItemId"/>
     <tableColumn id="9" name="UpgradeRequiredItemCount"/>
@@ -456,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.875" customWidth="1"/>
@@ -468,7 +501,7 @@
     <col min="9" max="9" width="27.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,16 +524,19 @@
         <v>22</v>
       </c>
       <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -522,8 +558,8 @@
       <c r="G2">
         <v>12</v>
       </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="H2" t="s">
+        <v>26</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -531,8 +567,11 @@
       <c r="J2">
         <v>0</v>
       </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2002</v>
       </c>
@@ -554,17 +593,20 @@
       <c r="G3">
         <v>17</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1002</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2003</v>
       </c>
@@ -586,17 +628,20 @@
       <c r="G4">
         <v>22</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1004</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2004</v>
       </c>
@@ -618,17 +663,20 @@
       <c r="G5">
         <v>27</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5">
         <v>15</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1006</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2005</v>
       </c>
@@ -650,17 +698,20 @@
       <c r="G6">
         <v>32</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6">
         <v>20</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>1008</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2006</v>
       </c>
@@ -682,17 +733,20 @@
       <c r="G7">
         <v>37</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7">
         <v>25</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>1010</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2007</v>
       </c>
@@ -714,13 +768,16 @@
       <c r="G8">
         <v>42</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="s">
         <v>30</v>
       </c>
       <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
         <v>1012</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>10000</v>
       </c>
     </row>
